--- a/data/2026-08/reporte_2026-08-31.xlsx
+++ b/data/2026-08/reporte_2026-08-31.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 Flujo Completo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Adjudicaciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📰 BORA Licitaciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ Riesgo Licitatorio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +417,2337 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>en_comprar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nro_proceso_comprar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metodo_cruce_tgn</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 27/23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416807/20260831</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>COPA S.R.L</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30711879850</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>$28.483.116,00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_muestra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 27/23</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2416807</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416807/20260831</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>COPA S.R.L</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30711879850</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>$28.483.116,00</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/VmpiT2gxN25mOUZSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA CUYO
+Licitación Pública 27/23
+Expediente Nº: EX-2023-01325092- -AFIP-SECFDVAFCE#SDGOAI Objeto de la contratación: Alquiler
+depósito de secuestros y</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>es_adjudicacion</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0615/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - ARMAS, ACCESORIOS, REPUESTOS Y MUNICIONES.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2416764</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416764/20260831</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0500/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2416765</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416765/20260831</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0584/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2416766</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416766/20260831</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0593/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2416767</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416767/20260831</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0607/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2416768</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416768/20260831</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0611/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2416769</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416769/20260831</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0616/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2416770</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416770/20260831</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0617/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2416771</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416771/20260831</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0622/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2416772</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416772/20260831</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BANCO CENTRAL DE LA REPÚBLICA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Licitación Pública 33/26</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. PROC. AUTOMATICO DE DATOS, SOFT., SUM.Y EQ. APOYO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2416773</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416773/20260831</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0337/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2416774</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416774/20260831</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0340/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2416775</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416775/20260831</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE BUENOS AIRES - HOSPITAL DE CLÍNICAS JOSÉ DE SAN MARTÍN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Licitación Pública 07/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2416776</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416776/20260831</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional 41-2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2416777</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416777/20260831</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0135/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS Y SUMINISTROS PARA LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2416778</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416778/20260831</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Licitación Pública 32/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - INMUEBLES</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2416779</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416779/20260831</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA AUSTRAL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Licitación Pública 19/26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - MUEBLES, ARTICULOS Y UTILES DE USO DOMESTICO</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2416780</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416780/20260831</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SECRETARÍA GENERAL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0016/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2416781</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416781/20260831</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0142/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2416782</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416782/20260831</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA PLATA - SECRETARÍA DE PLANEAMIENTO, OBRAS Y SERVICIOS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Licitación Pública 09/26</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2416783</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416783/20260831</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PREFECTURA NAVAL ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0036/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2416784</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416784/20260831</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE SALTA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Licitación Pública 02/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SEGUROS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2416785</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416785/20260831</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AUDITORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Licitación Pública 12/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SEGUROS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2416786</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416786/20260831</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN GENERAL DE PUERTOS S.A.U.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Licitación Pública 12/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DE CONTROL DE PLAGAS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2416787</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416787/20260831</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SECRETARÍA DE CULTURA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0003/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2416788</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416788/20260831</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0004/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2416789</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416789/20260831</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SANIDAD Y CALIDAD AGROALIMENTARIA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0027/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2416790</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416790/20260831</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LUJÁN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Licitación Pública 003/26</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2416791</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416791/20260831</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0137/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2416792</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416792/20260831</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0501/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2416793</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416793/20260831</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN GENERAL DE PUERTOS S.A.U.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Licitación Pública 13/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2416794</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416794/20260831</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AUDITORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Licitación Pública 13/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2416795</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416795/20260831</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FUERZA AÉREA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Licitación Pública 139/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2416796</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416796/20260831</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA AUSTRAL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Licitación Pública 18/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2416797</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416797/20260831</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>BANCO CENTRAL DE LA REPÚBLICA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Licitación Pública 28/26</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2416798</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416798/20260831</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE RELACIONES EXTERIORES, COMERCIO INTERNACIONAL Y CULTO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Licitación Pública 5/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2416799</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416799/20260831</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Licitación Pública 558/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2416800</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416800/20260831</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA PLATA - SECRETARÍA DE PLANEAMIENTO, OBRAS Y SERVICIOS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Licitación Pública 8/26</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2416801</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416801/20260831</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HONORABLE SENADO DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Licitación Pública 9/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2416802</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416802/20260831</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Subasta Pública 392-0056-SPU25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - VARIOS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2416803</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416803/20260831</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AGENCIA DE ADMINISTRACIÓN DE BIENES DEL ESTADO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Subasta Pública 392-0070-SPU26</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>VENTAS Y OFRECIMIENTOS DEL ESTADO - VARIOS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2416804</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416804/20260831</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FABRICACIONES MILITARES SOCIEDAD ANÓNIMA UNIPERSONAL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Concurso Público CPU-2026-SC-001</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>VARIOS - VARIOS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2416805</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416805/20260831</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0315/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LOCACIONES - VARIOS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2416806</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416806/20260831</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1030,4 +3365,138 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 27/23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30711879850</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>$28.483.116,00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2416807/20260831</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>